--- a/artfynd/A 58557-2025 artfynd.xlsx
+++ b/artfynd/A 58557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61570061</v>
+        <v>61570054</v>
       </c>
       <c r="B2" t="n">
-        <v>87997</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1596</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751631.0090383544</v>
+        <v>751613</v>
       </c>
       <c r="R2" t="n">
-        <v>7366490.942541964</v>
+        <v>7366628</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +753,9 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,41 +787,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61570056</v>
+        <v>61570059</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751613.4003591199</v>
+        <v>751631</v>
       </c>
       <c r="R3" t="n">
-        <v>7366627.98007447</v>
+        <v>7366491</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +865,9 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61570059</v>
+        <v>114045743</v>
       </c>
       <c r="B4" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,30 +927,20 @@
           <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Görjeån, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751631.0090383544</v>
+        <v>751591</v>
       </c>
       <c r="R4" t="n">
-        <v>7366490.942541964</v>
+        <v>7366710</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,38 +978,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61570054</v>
+        <v>114494557</v>
       </c>
       <c r="B5" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,30 +1024,23 @@
           <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Kilkok 8, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751613.4003591199</v>
+        <v>751670</v>
       </c>
       <c r="R5" t="n">
-        <v>7366627.98007447</v>
+        <v>7366618</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,22 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,74 +1082,76 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>med Överståndare</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>61570055</v>
+        <v>114500640</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kilkokheden, Lu lm</t>
+          <t>Kilkok 11, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751613.4003591199</v>
+        <v>751587</v>
       </c>
       <c r="R6" t="n">
-        <v>7366627.98007447</v>
+        <v>7366488</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,22 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,34 +1193,35 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>med Överståndare</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Sundberg, Sonja Kuoljok</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114045725</v>
+        <v>61570061</v>
       </c>
       <c r="B7" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,37 +1229,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>1596</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751594</v>
+        <v>751631</v>
       </c>
       <c r="R7" t="n">
-        <v>7366449</v>
+        <v>7366491</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,12 +1293,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,55 +1307,55 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114045712</v>
+        <v>114045756</v>
       </c>
       <c r="B8" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1436,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751582</v>
+        <v>751550</v>
       </c>
       <c r="R8" t="n">
-        <v>7366449</v>
+        <v>7366434</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,12 +1430,7 @@
         <v>114045770</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,53 +1524,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114045746</v>
+        <v>61569837</v>
       </c>
       <c r="B10" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751674</v>
+        <v>751563</v>
       </c>
       <c r="R10" t="n">
-        <v>7366668</v>
+        <v>7366563</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1599,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,71 +1613,73 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nils Bodin</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114483407</v>
+        <v>61570056</v>
       </c>
       <c r="B11" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kilkok 5, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751598</v>
+        <v>751613</v>
       </c>
       <c r="R11" t="n">
-        <v>7366516</v>
+        <v>7366628</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1786,38 +1717,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114500640</v>
+        <v>114500638</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,14 +1774,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kilkok 11, Lu lm</t>
+          <t>Kilkok 12, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751587</v>
+        <v>751550</v>
       </c>
       <c r="R12" t="n">
-        <v>7366488</v>
+        <v>7366445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,56 +1851,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114494557</v>
+        <v>61569840</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kilkok 8, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751670</v>
+        <v>751563</v>
       </c>
       <c r="R13" t="n">
-        <v>7366618</v>
+        <v>7366563</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,12 +1918,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,81 +1936,69 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>med Överståndare</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114494570</v>
+        <v>61570055</v>
       </c>
       <c r="B14" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kilkok 6, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751571</v>
+        <v>751613</v>
       </c>
       <c r="R14" t="n">
-        <v>7366489</v>
+        <v>7366628</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2114,12 +2022,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,28 +2040,951 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>med Överståndare</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>61569841</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kilkokheden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>751563</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7366563</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>61569845</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kilkokheden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>751563</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7366563</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114045712</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>751582</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7366449</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114045725</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>751594</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7366449</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114045739</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>751540</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7366417</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114045746</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>751674</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7366668</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Nils Bodin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114483407</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kilkok 5, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>751598</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7366516</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114494570</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kilkok 6, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>751571</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7366489</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>med Överståndare</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>61590681</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kilkokheden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>751631</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7366491</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2016-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2016-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
